--- a/artfynd/S 1160-2024 artfynd.xlsx
+++ b/artfynd/S 1160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY376"/>
+  <dimension ref="A1:AZ376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122471854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105009185</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128235068</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115183808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121597897</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122441328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590078</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111983757</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,6 +1892,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,6 +2018,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536192</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2071,6 +2131,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588686</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2179,6 +2244,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588973</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2385,6 +2460,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104977865</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986970</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2579,6 +2664,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986971</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986972</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2784,6 +2879,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110677827</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110678488</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3000,6 +3105,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111447026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3118,6 +3228,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269951</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3245,6 +3360,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365387</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3372,6 +3492,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112367310</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3499,6 +3624,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680381</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3616,6 +3746,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112736567</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3738,6 +3873,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112736803</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3856,6 +3996,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112736968</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3978,6 +4123,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922289</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4096,6 +4246,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922367</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4214,6 +4369,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112922467</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4336,6 +4496,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113123090</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4463,6 +4628,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113693120</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4585,6 +4755,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113693188</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4706,6 +4881,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115246353</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4832,6 +5012,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115246905</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4939,6 +5124,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954428</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5046,6 +5236,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954430</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5158,6 +5353,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954438</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5265,6 +5465,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954439</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5372,6 +5577,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954443</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5479,6 +5689,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954451</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5600,6 +5815,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118321095</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5721,6 +5941,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118761156</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5847,6 +6072,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118761478</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5968,6 +6198,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118761721</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6089,6 +6324,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762265</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6210,6 +6450,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603400</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6311,6 +6556,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431512</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6419,6 +6669,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111978312</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6527,6 +6782,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111978645</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6649,6 +6909,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112679208</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6771,6 +7036,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112679426</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6893,6 +7163,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112736316</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7015,6 +7290,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112911140</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7136,6 +7416,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128517676</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7257,6 +7542,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875824</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7367,6 +7657,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129106629</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7488,6 +7783,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129180982</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7609,6 +7909,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129182020</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7730,6 +8035,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238044</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7827,6 +8137,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986947</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7924,6 +8239,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986948</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8021,6 +8341,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986949</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8143,6 +8468,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365809</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8264,6 +8594,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128122397</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8385,6 +8720,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405584</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8506,6 +8846,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532349</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8614,6 +8959,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589737</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8736,6 +9086,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112052487</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8857,6 +9212,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128057655</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8978,6 +9338,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128406849</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9099,6 +9464,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532867</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9207,6 +9577,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589111</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9315,6 +9690,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589112</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9423,6 +9803,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589752</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9531,6 +9916,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589759</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9643,6 +10033,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307497</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9770,6 +10165,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112265707</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9897,6 +10297,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366031</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10024,6 +10429,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680830</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10151,6 +10561,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112735181</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10278,6 +10693,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112737115</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10405,6 +10825,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923951</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10532,6 +10957,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114481171</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10658,6 +11088,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128251860</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10784,6 +11219,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128403977</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10910,6 +11350,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404671</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11036,6 +11481,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128517298</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11162,6 +11612,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518197</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11288,6 +11743,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532762</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11414,6 +11874,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556706</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11540,6 +12005,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128557641</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11669,6 +12139,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876603</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11795,6 +12270,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938263</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11921,6 +12401,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128938378</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12047,6 +12532,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990963</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12173,6 +12663,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994306</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12299,6 +12794,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129088292</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12413,6 +12913,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129106226</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12527,6 +13032,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107832</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12648,6 +13158,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129201104</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12769,6 +13284,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129201660</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12895,6 +13415,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132716786</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13021,6 +13546,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307945</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13147,6 +13677,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128403857</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13263,6 +13798,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107633</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13385,6 +13925,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112391684</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13511,6 +14056,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128123625</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13619,6 +14169,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588676</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13741,6 +14296,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114432126</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13862,6 +14422,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115244591</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13983,6 +14548,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115367182</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14109,6 +14679,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115889742</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14236,6 +14811,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954437</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14362,6 +14942,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604666</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14483,6 +15068,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128057835</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14604,6 +15194,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404146</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14725,6 +15320,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129162296</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14833,6 +15433,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590320</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14941,6 +15546,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593107</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15049,6 +15659,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104779245</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15157,6 +15772,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104978112</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15259,6 +15879,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986952</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15356,6 +15981,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986953</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15468,6 +16098,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106168708</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15576,6 +16211,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111717141</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15698,6 +16338,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113420380</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15820,6 +16465,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113420416</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15942,6 +16592,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114538666</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16063,6 +16718,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228551</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16184,6 +16844,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229510</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16305,6 +16970,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115266479</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16426,6 +17096,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116362672</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16553,6 +17228,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954433</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16680,6 +17360,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954441</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16811,6 +17496,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954452</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16932,6 +17622,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762326</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17053,6 +17748,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121897567</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17174,6 +17874,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122271737</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17295,6 +18000,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122271768</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17416,6 +18126,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122271933</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17537,6 +18252,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440986</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17658,6 +18378,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122441106</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17779,6 +18504,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122441729</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17880,6 +18610,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431511</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17988,6 +18723,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104977993</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -18096,6 +18836,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593141</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18213,6 +18958,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111979907</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18340,6 +19090,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269619</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18462,6 +19217,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269746</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18583,6 +19343,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128403615</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18704,6 +19469,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518074</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18825,6 +19595,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532532</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18946,6 +19721,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875689</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -19067,6 +19847,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992888</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -19188,6 +19973,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341062</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19310,6 +20100,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112049400</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19424,6 +20219,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129108665</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19532,6 +20332,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589368</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19640,6 +20445,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590403</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19748,6 +20558,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590407</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19865,6 +20680,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111981282</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19987,6 +20807,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111984081</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -20111,6 +20936,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112264849</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -20233,6 +21063,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365143</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20355,6 +21190,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112367427</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20477,6 +21317,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112367469</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20603,6 +21448,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112733332</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20725,6 +21575,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112733428</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20852,6 +21707,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112734498</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20974,6 +21834,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112734917</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21096,6 +21961,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112735262</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -21218,6 +22088,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112735374</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21340,6 +22215,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112735955</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21457,6 +22337,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112816348</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21579,6 +22464,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112844470</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21701,6 +22591,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845099</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21823,6 +22718,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982125</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21945,6 +22845,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178881</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -22066,6 +22971,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307498</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -22187,6 +23097,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307615</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22313,6 +23228,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128308274</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22439,6 +23359,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404021</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22560,6 +23485,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405661</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22686,6 +23616,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408163</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22807,6 +23742,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128517373</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22928,6 +23868,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518112</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -23049,6 +23994,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518224</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -23170,6 +24120,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518311</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23291,6 +24246,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518381</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23412,6 +24372,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518453</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23533,6 +24498,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518473</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23654,6 +24624,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128531972</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23775,6 +24750,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532089</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23896,6 +24876,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532173</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -24017,6 +25002,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532377</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -24138,6 +25128,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533102</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -24259,6 +25254,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533484</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24385,6 +25385,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533510</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24506,6 +25511,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535083</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24632,6 +25642,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535204</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24753,6 +25768,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535591</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24874,6 +25894,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535711</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24995,6 +26020,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536017</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25116,6 +26146,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536441</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25237,6 +26272,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536478</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25358,6 +26398,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555153</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25479,6 +26524,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555330</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25600,6 +26650,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555412</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25721,6 +26776,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555457</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25842,6 +26902,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555554</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25963,6 +27028,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555690</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -26084,6 +27154,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555769</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26205,6 +27280,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555961</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -26326,6 +27406,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556060</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -26447,6 +27532,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556176</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26568,6 +27658,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556263</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26689,6 +27784,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556336</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26810,6 +27910,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128557738</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26931,6 +28036,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128558190</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -27052,6 +28162,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128558286</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -27173,6 +28288,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875503</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -27294,6 +28414,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876010</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -27415,6 +28540,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876049</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -27536,6 +28666,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876246</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27662,6 +28797,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876318</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27783,6 +28923,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876478</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -27904,6 +29049,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876930</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -28025,6 +29175,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877104</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -28146,6 +29301,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877134</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -28267,6 +29427,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877240</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -28388,6 +29553,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936232</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -28509,6 +29679,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936815</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -28630,6 +29805,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937342</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28751,6 +29931,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940047</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28872,6 +30057,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940096</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -28993,6 +30183,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940384</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -29114,6 +30309,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940569</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -29235,6 +30435,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990729</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -29356,6 +30561,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990882</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -29477,6 +30687,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990903</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -29598,6 +30813,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991106</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29719,6 +30939,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991152</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29840,6 +31065,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991210</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -29961,6 +31191,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128991603</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -30082,6 +31317,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992322</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30203,6 +31443,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992436</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -30324,6 +31569,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128992654</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -30445,6 +31695,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993013</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -30566,6 +31821,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128993526</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -30687,6 +31947,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994376</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -30808,6 +32073,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994633</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30929,6 +32199,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129089144</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -31043,6 +32318,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129108358</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -31164,6 +32444,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129181650</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -31285,6 +32570,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129181735</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -31406,6 +32696,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129182684</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -31527,6 +32822,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129182808</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -31648,6 +32948,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129200452</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -31769,6 +33074,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129200619</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -31890,6 +33200,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129200975</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -32011,6 +33326,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129202361</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -32132,6 +33452,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129202480</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -32253,6 +33578,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226728</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -32374,6 +33704,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237526</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -32482,6 +33817,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112264965</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -32603,6 +33943,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603285</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -32724,6 +34069,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128122067</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -32845,6 +34195,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405161</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32966,6 +34321,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936668</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -33078,6 +34438,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123372765</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -33186,6 +34551,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588793</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -33288,6 +34658,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986960</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -33385,6 +34760,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105009186</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -33493,6 +34873,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589257</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -33601,6 +34986,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590316</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -33709,6 +35099,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104592860</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -33817,6 +35212,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593056</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33914,6 +35314,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986950</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -34011,6 +35416,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105009183</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -34128,6 +35538,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115397165</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -34255,6 +35670,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954431</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -34377,6 +35797,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954432</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -34499,6 +35924,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954435</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -34621,6 +36051,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954436</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -34748,6 +36183,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954444</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -34878,6 +36318,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954449</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -35005,6 +36450,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954450</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -35121,6 +36571,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589158</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -35237,6 +36692,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589793</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -35339,6 +36799,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986956</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -35466,6 +36931,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113917339</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -35593,6 +37063,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114432353</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -35710,6 +37185,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954453</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -35832,6 +37312,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128940336</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -35953,6 +37438,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990801</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -36075,6 +37565,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129199568</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -36201,6 +37696,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129199903</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -36322,6 +37822,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115135238</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -36438,6 +37943,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228797</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -36559,6 +38069,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115246177</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -36670,6 +38185,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954447</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -36780,6 +38300,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115137555</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -36897,6 +38422,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115244459</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -37009,6 +38539,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115245139</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -37126,6 +38661,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115246093</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -37243,6 +38783,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115247038</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -37360,6 +38905,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268520</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -37477,6 +39027,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115268867</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -37594,6 +39149,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115344082</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -37711,6 +39271,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115365937</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -37828,6 +39393,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115366633</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -37945,6 +39515,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115367128</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -38062,6 +39637,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115367658</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -38179,6 +39759,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115368068</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -38296,6 +39881,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115368265</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -38413,6 +40003,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115368614</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -38530,6 +40125,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115394243</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -38647,6 +40247,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115883408</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -38764,6 +40369,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115883741</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -38881,6 +40491,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115884155</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -38998,6 +40613,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115885136</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -39115,6 +40735,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115889484</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -39232,6 +40857,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115889564</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -39349,6 +40979,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115889930</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -39466,6 +41101,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115890079</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -39583,6 +41223,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116083617</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -39700,6 +41345,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084059</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -39817,6 +41467,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116133978</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -39934,6 +41589,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116134631</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -40055,6 +41715,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116361177</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -40172,6 +41837,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116362592</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -40289,6 +41959,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116363213</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -40406,6 +42081,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116363979</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -40523,6 +42203,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121762673</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -40640,6 +42325,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440603</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -40757,6 +42447,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440837</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -40874,6 +42569,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123245840</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -40991,6 +42691,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123246008</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -41108,6 +42813,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123246366</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -41225,6 +42935,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123247686</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -41342,6 +43057,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452616</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -41454,6 +43174,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123453886</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -41566,6 +43291,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663726</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -41678,6 +43408,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287484</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -41795,6 +43530,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287812</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -41912,6 +43652,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124602837</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -42024,6 +43769,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124603038</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -42141,6 +43891,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124603380</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -42258,6 +44013,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124606406</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -42371,6 +44131,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589323</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -42468,6 +44233,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986969</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -42580,6 +44350,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954454</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -42688,6 +44463,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590376</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -42820,6 +44600,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954423</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -42932,6 +44717,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287073</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -43040,6 +44830,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588894</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -43147,6 +44942,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954456</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -43255,6 +45055,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588893</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -43367,6 +45172,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339959</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -43483,6 +45293,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133222014</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -43615,6 +45430,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954429</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -43747,6 +45567,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954459</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -43879,6 +45704,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954455</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -43990,6 +45820,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164423</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -44111,6 +45946,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128994491</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -44237,6 +46077,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126198336</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -44345,6 +46190,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104589382</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -44453,6 +46303,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593080</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -44561,6 +46416,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593123</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -44682,6 +46542,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451129</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -44789,6 +46654,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954427</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -44896,6 +46766,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954457</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -45006,8 +46881,390 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129106452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>